--- a/Team-Data/2008-09/3-27-2008-09.xlsx
+++ b/Team-Data/2008-09/3-27-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,28 +728,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E2" t="n">
         <v>42</v>
       </c>
       <c r="F2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G2" t="n">
-        <v>0.575</v>
+        <v>0.583</v>
       </c>
       <c r="H2" t="n">
         <v>48.1</v>
       </c>
       <c r="I2" t="n">
-        <v>36.3</v>
+        <v>36.4</v>
       </c>
       <c r="J2" t="n">
-        <v>79</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>0.46</v>
+        <v>0.461</v>
       </c>
       <c r="L2" t="n">
         <v>7.3</v>
@@ -697,13 +764,13 @@
         <v>18.3</v>
       </c>
       <c r="P2" t="n">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="Q2" t="n">
         <v>0.732</v>
       </c>
       <c r="R2" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="S2" t="n">
         <v>29.5</v>
@@ -712,7 +779,7 @@
         <v>40.2</v>
       </c>
       <c r="U2" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="V2" t="n">
         <v>12.8</v>
@@ -724,22 +791,22 @@
         <v>4.7</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Z2" t="n">
         <v>19.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AB2" t="n">
-        <v>98.3</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AD2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE2" t="n">
         <v>12</v>
@@ -769,13 +836,13 @@
         <v>7</v>
       </c>
       <c r="AN2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AQ2" t="n">
         <v>29</v>
@@ -802,13 +869,13 @@
         <v>18</v>
       </c>
       <c r="AY2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ2" t="n">
         <v>5</v>
       </c>
       <c r="BA2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BB2" t="n">
         <v>17</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-27-2008-09</t>
+          <t>2009-03-27</t>
         </is>
       </c>
     </row>
@@ -858,52 +925,52 @@
         <v>48.4</v>
       </c>
       <c r="I3" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J3" t="n">
-        <v>77</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K3" t="n">
         <v>0.485</v>
       </c>
       <c r="L3" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M3" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="N3" t="n">
-        <v>0.395</v>
+        <v>0.392</v>
       </c>
       <c r="O3" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="P3" t="n">
-        <v>25.5</v>
+        <v>25.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.771</v>
+        <v>0.769</v>
       </c>
       <c r="R3" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="S3" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T3" t="n">
-        <v>42.5</v>
+        <v>42.3</v>
       </c>
       <c r="U3" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="V3" t="n">
         <v>15.7</v>
       </c>
       <c r="W3" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="X3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y3" t="n">
         <v>4.7</v>
@@ -912,10 +979,10 @@
         <v>23.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>100.9</v>
+        <v>100.8</v>
       </c>
       <c r="AC3" t="n">
         <v>8.1</v>
@@ -945,7 +1012,7 @@
         <v>2</v>
       </c>
       <c r="AL3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM3" t="n">
         <v>21</v>
@@ -954,37 +1021,37 @@
         <v>1</v>
       </c>
       <c r="AO3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AR3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS3" t="n">
         <v>5</v>
       </c>
       <c r="AT3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU3" t="n">
         <v>4</v>
       </c>
       <c r="AV3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AW3" t="n">
         <v>7</v>
       </c>
       <c r="AX3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AY3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ3" t="n">
         <v>27</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-27-2008-09</t>
+          <t>2009-03-27</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F4" t="n">
         <v>40</v>
       </c>
       <c r="G4" t="n">
-        <v>0.444</v>
+        <v>0.437</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
@@ -1043,10 +1110,10 @@
         <v>34.9</v>
       </c>
       <c r="J4" t="n">
-        <v>76.59999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="K4" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L4" t="n">
         <v>6</v>
@@ -1055,19 +1122,19 @@
         <v>16.2</v>
       </c>
       <c r="N4" t="n">
-        <v>0.369</v>
+        <v>0.37</v>
       </c>
       <c r="O4" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="P4" t="n">
         <v>23.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.741</v>
+        <v>0.742</v>
       </c>
       <c r="R4" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S4" t="n">
         <v>28.8</v>
@@ -1088,7 +1155,7 @@
         <v>4.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Z4" t="n">
         <v>21.7</v>
@@ -1097,13 +1164,13 @@
         <v>20.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>93.59999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1</v>
+        <v>-1.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AE4" t="n">
         <v>18</v>
@@ -1115,7 +1182,7 @@
         <v>18</v>
       </c>
       <c r="AH4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI4" t="n">
         <v>29</v>
@@ -1148,7 +1215,7 @@
         <v>17</v>
       </c>
       <c r="AS4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT4" t="n">
         <v>27</v>
@@ -1157,10 +1224,10 @@
         <v>12</v>
       </c>
       <c r="AV4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX4" t="n">
         <v>14</v>
@@ -1172,7 +1239,7 @@
         <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB4" t="n">
         <v>29</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-27-2008-09</t>
+          <t>2009-03-27</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F5" t="n">
         <v>38</v>
       </c>
       <c r="G5" t="n">
-        <v>0.472</v>
+        <v>0.479</v>
       </c>
       <c r="H5" t="n">
         <v>48.6</v>
@@ -1225,10 +1292,10 @@
         <v>37.8</v>
       </c>
       <c r="J5" t="n">
-        <v>83.5</v>
+        <v>83.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0.453</v>
+        <v>0.454</v>
       </c>
       <c r="L5" t="n">
         <v>6</v>
@@ -1237,16 +1304,16 @@
         <v>15.7</v>
       </c>
       <c r="N5" t="n">
-        <v>0.38</v>
+        <v>0.381</v>
       </c>
       <c r="O5" t="n">
-        <v>19.7</v>
+        <v>19.9</v>
       </c>
       <c r="P5" t="n">
-        <v>24.8</v>
+        <v>25.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.793</v>
+        <v>0.792</v>
       </c>
       <c r="R5" t="n">
         <v>12.1</v>
@@ -1258,34 +1325,34 @@
         <v>42.6</v>
       </c>
       <c r="U5" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="V5" t="n">
         <v>14.9</v>
       </c>
       <c r="W5" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X5" t="n">
         <v>5.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Z5" t="n">
         <v>21.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>101.3</v>
+        <v>101.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.9</v>
+        <v>-0.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AE5" t="n">
         <v>16</v>
@@ -1294,10 +1361,10 @@
         <v>17</v>
       </c>
       <c r="AG5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI5" t="n">
         <v>8</v>
@@ -1309,7 +1376,7 @@
         <v>19</v>
       </c>
       <c r="AL5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM5" t="n">
         <v>24</v>
@@ -1318,10 +1385,10 @@
         <v>6</v>
       </c>
       <c r="AO5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AP5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AQ5" t="n">
         <v>7</v>
@@ -1330,7 +1397,7 @@
         <v>6</v>
       </c>
       <c r="AS5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT5" t="n">
         <v>7</v>
@@ -1339,7 +1406,7 @@
         <v>15</v>
       </c>
       <c r="AV5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW5" t="n">
         <v>12</v>
@@ -1354,13 +1421,13 @@
         <v>19</v>
       </c>
       <c r="BA5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BB5" t="n">
         <v>10</v>
       </c>
       <c r="BC5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-27-2008-09</t>
+          <t>2009-03-27</t>
         </is>
       </c>
     </row>
@@ -1392,58 +1459,58 @@
         <v>71</v>
       </c>
       <c r="E6" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6" t="n">
-        <v>0.831</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="H6" t="n">
         <v>48.2</v>
       </c>
       <c r="I6" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J6" t="n">
-        <v>78.3</v>
+        <v>78.2</v>
       </c>
       <c r="K6" t="n">
-        <v>0.47</v>
+        <v>0.469</v>
       </c>
       <c r="L6" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="M6" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0.392</v>
+        <v>0.388</v>
       </c>
       <c r="O6" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="P6" t="n">
-        <v>24.9</v>
+        <v>25.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.756</v>
+        <v>0.754</v>
       </c>
       <c r="R6" t="n">
         <v>10.7</v>
       </c>
       <c r="S6" t="n">
-        <v>31.2</v>
+        <v>31.1</v>
       </c>
       <c r="T6" t="n">
-        <v>41.9</v>
+        <v>41.8</v>
       </c>
       <c r="U6" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V6" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="W6" t="n">
         <v>7.5</v>
@@ -1455,19 +1522,19 @@
         <v>4</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>100.5</v>
+        <v>100.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1482,7 +1549,7 @@
         <v>23</v>
       </c>
       <c r="AI6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ6" t="n">
         <v>25</v>
@@ -1491,22 +1558,22 @@
         <v>5</v>
       </c>
       <c r="AL6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AM6" t="n">
         <v>5</v>
       </c>
       <c r="AN6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AQ6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR6" t="n">
         <v>18</v>
@@ -1515,10 +1582,10 @@
         <v>9</v>
       </c>
       <c r="AT6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AU6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AV6" t="n">
         <v>7</v>
@@ -1536,7 +1603,7 @@
         <v>7</v>
       </c>
       <c r="BA6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BB6" t="n">
         <v>12</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-27-2008-09</t>
+          <t>2009-03-27</t>
         </is>
       </c>
     </row>
@@ -1571,61 +1638,61 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E7" t="n">
         <v>43</v>
       </c>
       <c r="F7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G7" t="n">
-        <v>0.597</v>
+        <v>0.606</v>
       </c>
       <c r="H7" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I7" t="n">
-        <v>38.1</v>
+        <v>38.2</v>
       </c>
       <c r="J7" t="n">
         <v>82.90000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.46</v>
+        <v>0.461</v>
       </c>
       <c r="L7" t="n">
         <v>6.8</v>
       </c>
       <c r="M7" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="N7" t="n">
-        <v>0.345</v>
+        <v>0.344</v>
       </c>
       <c r="O7" t="n">
-        <v>18.4</v>
+        <v>18.2</v>
       </c>
       <c r="P7" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="S7" t="n">
-        <v>31.6</v>
+        <v>31.8</v>
       </c>
       <c r="T7" t="n">
         <v>42.9</v>
       </c>
       <c r="U7" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="V7" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="W7" t="n">
         <v>7.3</v>
@@ -1640,16 +1707,16 @@
         <v>19.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
       <c r="AB7" t="n">
         <v>101.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AE7" t="n">
         <v>11</v>
@@ -1670,19 +1737,19 @@
         <v>6</v>
       </c>
       <c r="AK7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AL7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM7" t="n">
         <v>8</v>
       </c>
       <c r="AN7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO7" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AP7" t="n">
         <v>28</v>
@@ -1691,7 +1758,7 @@
         <v>2</v>
       </c>
       <c r="AR7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AS7" t="n">
         <v>6</v>
@@ -1700,16 +1767,16 @@
         <v>6</v>
       </c>
       <c r="AU7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX7" t="n">
         <v>10</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>8</v>
       </c>
       <c r="AY7" t="n">
         <v>8</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-27-2008-09</t>
+          <t>2009-03-27</t>
         </is>
       </c>
     </row>
@@ -1753,28 +1820,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E8" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F8" t="n">
         <v>26</v>
       </c>
       <c r="G8" t="n">
-        <v>0.644</v>
+        <v>0.639</v>
       </c>
       <c r="H8" t="n">
         <v>48.1</v>
       </c>
       <c r="I8" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J8" t="n">
-        <v>79.09999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="K8" t="n">
-        <v>0.467</v>
+        <v>0.466</v>
       </c>
       <c r="L8" t="n">
         <v>6.4</v>
@@ -1786,16 +1853,16 @@
         <v>0.367</v>
       </c>
       <c r="O8" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="P8" t="n">
-        <v>30.3</v>
+        <v>30.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.761</v>
+        <v>0.762</v>
       </c>
       <c r="R8" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="S8" t="n">
         <v>30.2</v>
@@ -1807,10 +1874,10 @@
         <v>21.9</v>
       </c>
       <c r="V8" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="W8" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X8" t="n">
         <v>5.9</v>
@@ -1819,10 +1886,10 @@
         <v>5.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="AB8" t="n">
         <v>103.5</v>
@@ -1831,22 +1898,22 @@
         <v>3.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF8" t="n">
         <v>6</v>
       </c>
       <c r="AG8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ8" t="n">
         <v>23</v>
@@ -1855,13 +1922,13 @@
         <v>6</v>
       </c>
       <c r="AL8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM8" t="n">
         <v>18</v>
       </c>
       <c r="AN8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1873,22 +1940,22 @@
         <v>20</v>
       </c>
       <c r="AR8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS8" t="n">
         <v>15</v>
       </c>
       <c r="AT8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX8" t="n">
         <v>3</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-27-2008-09</t>
+          <t>2009-03-27</t>
         </is>
       </c>
     </row>
@@ -2013,25 +2080,25 @@
         <v>-0.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AE9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF9" t="n">
         <v>16</v>
       </c>
       <c r="AG9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI9" t="n">
         <v>22</v>
       </c>
       <c r="AJ9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AK9" t="n">
         <v>18</v>
@@ -2043,7 +2110,7 @@
         <v>29</v>
       </c>
       <c r="AN9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO9" t="n">
         <v>29</v>
@@ -2058,7 +2125,7 @@
         <v>11</v>
       </c>
       <c r="AS9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT9" t="n">
         <v>18</v>
@@ -2067,16 +2134,16 @@
         <v>16</v>
       </c>
       <c r="AV9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW9" t="n">
         <v>29</v>
       </c>
       <c r="AX9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ9" t="n">
         <v>18</v>
@@ -2088,7 +2155,7 @@
         <v>28</v>
       </c>
       <c r="BC9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-27-2008-09</t>
+          <t>2009-03-27</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-3.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE10" t="n">
         <v>24</v>
@@ -2216,7 +2283,7 @@
         <v>3</v>
       </c>
       <c r="AK10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL10" t="n">
         <v>16</v>
@@ -2249,7 +2316,7 @@
         <v>14</v>
       </c>
       <c r="AV10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW10" t="n">
         <v>6</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-27-2008-09</t>
+          <t>2009-03-27</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2447,7 @@
         <v>1</v>
       </c>
       <c r="AE11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF11" t="n">
         <v>6</v>
@@ -2389,7 +2456,7 @@
         <v>6</v>
       </c>
       <c r="AH11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI11" t="n">
         <v>27</v>
@@ -2410,7 +2477,7 @@
         <v>9</v>
       </c>
       <c r="AO11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP11" t="n">
         <v>20</v>
@@ -2425,13 +2492,13 @@
         <v>2</v>
       </c>
       <c r="AT11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU11" t="n">
         <v>19</v>
       </c>
       <c r="AV11" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AW11" t="n">
         <v>25</v>
@@ -2446,10 +2513,10 @@
         <v>2</v>
       </c>
       <c r="BA11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC11" t="n">
         <v>7</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-27-2008-09</t>
+          <t>2009-03-27</t>
         </is>
       </c>
     </row>
@@ -2559,16 +2626,16 @@
         <v>-1.9</v>
       </c>
       <c r="AD12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE12" t="n">
         <v>20</v>
       </c>
       <c r="AF12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH12" t="n">
         <v>11</v>
@@ -2580,10 +2647,10 @@
         <v>2</v>
       </c>
       <c r="AK12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM12" t="n">
         <v>3</v>
@@ -2592,10 +2659,10 @@
         <v>10</v>
       </c>
       <c r="AO12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ12" t="n">
         <v>5</v>
@@ -2616,7 +2683,7 @@
         <v>20</v>
       </c>
       <c r="AW12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX12" t="n">
         <v>9</v>
@@ -2625,7 +2692,7 @@
         <v>26</v>
       </c>
       <c r="AZ12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA12" t="n">
         <v>13</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-27-2008-09</t>
+          <t>2009-03-27</t>
         </is>
       </c>
     </row>
@@ -2663,28 +2730,28 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E13" t="n">
         <v>18</v>
       </c>
       <c r="F13" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G13" t="n">
-        <v>0.247</v>
+        <v>0.25</v>
       </c>
       <c r="H13" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I13" t="n">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="J13" t="n">
         <v>81.8</v>
       </c>
       <c r="K13" t="n">
-        <v>0.441</v>
+        <v>0.44</v>
       </c>
       <c r="L13" t="n">
         <v>6.6</v>
@@ -2693,16 +2760,16 @@
         <v>18.3</v>
       </c>
       <c r="N13" t="n">
-        <v>0.36</v>
+        <v>0.358</v>
       </c>
       <c r="O13" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="P13" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.742</v>
+        <v>0.743</v>
       </c>
       <c r="R13" t="n">
         <v>11</v>
@@ -2714,13 +2781,13 @@
         <v>39.9</v>
       </c>
       <c r="U13" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="V13" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W13" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="X13" t="n">
         <v>5.9</v>
@@ -2729,19 +2796,19 @@
         <v>5.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AA13" t="n">
         <v>19.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>-8.5</v>
+        <v>-8.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE13" t="n">
         <v>27</v>
@@ -2750,7 +2817,7 @@
         <v>28</v>
       </c>
       <c r="AG13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AH13" t="n">
         <v>7</v>
@@ -2762,7 +2829,7 @@
         <v>10</v>
       </c>
       <c r="AK13" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AL13" t="n">
         <v>17</v>
@@ -2777,7 +2844,7 @@
         <v>28</v>
       </c>
       <c r="AP13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ13" t="n">
         <v>27</v>
@@ -2786,10 +2853,10 @@
         <v>16</v>
       </c>
       <c r="AS13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT13" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AU13" t="n">
         <v>13</v>
@@ -2798,7 +2865,7 @@
         <v>23</v>
       </c>
       <c r="AW13" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AX13" t="n">
         <v>2</v>
@@ -2807,7 +2874,7 @@
         <v>21</v>
       </c>
       <c r="AZ13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BA13" t="n">
         <v>26</v>
@@ -2816,7 +2883,7 @@
         <v>26</v>
       </c>
       <c r="BC13" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-27-2008-09</t>
+          <t>2009-03-27</t>
         </is>
       </c>
     </row>
@@ -2860,10 +2927,10 @@
         <v>48.3</v>
       </c>
       <c r="I14" t="n">
-        <v>40.8</v>
+        <v>40.7</v>
       </c>
       <c r="J14" t="n">
-        <v>85.3</v>
+        <v>85.2</v>
       </c>
       <c r="K14" t="n">
         <v>0.478</v>
@@ -2872,10 +2939,10 @@
         <v>6.8</v>
       </c>
       <c r="M14" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0.365</v>
+        <v>0.368</v>
       </c>
       <c r="O14" t="n">
         <v>19.7</v>
@@ -2884,19 +2951,19 @@
         <v>25.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.769</v>
+        <v>0.77</v>
       </c>
       <c r="R14" t="n">
         <v>12.4</v>
       </c>
       <c r="S14" t="n">
-        <v>31.5</v>
+        <v>31.7</v>
       </c>
       <c r="T14" t="n">
-        <v>44</v>
+        <v>44.2</v>
       </c>
       <c r="U14" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="V14" t="n">
         <v>13.6</v>
@@ -2914,16 +2981,16 @@
         <v>20.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>108.1</v>
+        <v>108</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD14" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
@@ -2953,19 +3020,19 @@
         <v>14</v>
       </c>
       <c r="AN14" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AO14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP14" t="n">
         <v>8</v>
       </c>
       <c r="AQ14" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AR14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS14" t="n">
         <v>7</v>
@@ -2980,16 +3047,16 @@
         <v>11</v>
       </c>
       <c r="AW14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AY14" t="n">
         <v>14</v>
       </c>
       <c r="AZ14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA14" t="n">
         <v>8</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-27-2008-09</t>
+          <t>2009-03-27</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F15" t="n">
         <v>53</v>
       </c>
       <c r="G15" t="n">
-        <v>0.254</v>
+        <v>0.243</v>
       </c>
       <c r="H15" t="n">
         <v>48.4</v>
@@ -3048,31 +3115,31 @@
         <v>77.40000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.45</v>
+        <v>0.449</v>
       </c>
       <c r="L15" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="M15" t="n">
         <v>13.3</v>
       </c>
       <c r="N15" t="n">
-        <v>0.352</v>
+        <v>0.348</v>
       </c>
       <c r="O15" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="P15" t="n">
-        <v>25.2</v>
+        <v>25.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.757</v>
+        <v>0.756</v>
       </c>
       <c r="R15" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="S15" t="n">
-        <v>28.4</v>
+        <v>28.3</v>
       </c>
       <c r="T15" t="n">
         <v>38.9</v>
@@ -3081,10 +3148,10 @@
         <v>17.2</v>
       </c>
       <c r="V15" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W15" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X15" t="n">
         <v>4.5</v>
@@ -3096,25 +3163,25 @@
         <v>21.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="AB15" t="n">
-        <v>93.40000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.2</v>
+        <v>-6.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AE15" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF15" t="n">
         <v>27</v>
       </c>
-      <c r="AF15" t="n">
-        <v>26</v>
-      </c>
       <c r="AG15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AH15" t="n">
         <v>14</v>
@@ -3126,7 +3193,7 @@
         <v>27</v>
       </c>
       <c r="AK15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL15" t="n">
         <v>27</v>
@@ -3135,19 +3202,19 @@
         <v>27</v>
       </c>
       <c r="AN15" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AO15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP15" t="n">
         <v>13</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>12</v>
       </c>
       <c r="AQ15" t="n">
         <v>22</v>
       </c>
       <c r="AR15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS15" t="n">
         <v>29</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-27-2008-09</t>
+          <t>2009-03-27</t>
         </is>
       </c>
     </row>
@@ -3287,22 +3354,22 @@
         <v>-0.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE16" t="n">
         <v>14</v>
       </c>
       <c r="AF16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH16" t="n">
         <v>1</v>
       </c>
       <c r="AI16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ16" t="n">
         <v>12</v>
@@ -3317,13 +3384,13 @@
         <v>10</v>
       </c>
       <c r="AN16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO16" t="n">
         <v>27</v>
       </c>
       <c r="AP16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ16" t="n">
         <v>21</v>
@@ -3350,7 +3417,7 @@
         <v>4</v>
       </c>
       <c r="AY16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ16" t="n">
         <v>16</v>
@@ -3359,7 +3426,7 @@
         <v>25</v>
       </c>
       <c r="BB16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC16" t="n">
         <v>15</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-27-2008-09</t>
+          <t>2009-03-27</t>
         </is>
       </c>
     </row>
@@ -3409,10 +3476,10 @@
         <v>36.5</v>
       </c>
       <c r="J17" t="n">
-        <v>82.3</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.443</v>
+        <v>0.445</v>
       </c>
       <c r="L17" t="n">
         <v>6.1</v>
@@ -3421,31 +3488,31 @@
         <v>16.8</v>
       </c>
       <c r="N17" t="n">
-        <v>0.362</v>
+        <v>0.363</v>
       </c>
       <c r="O17" t="n">
         <v>20</v>
       </c>
       <c r="P17" t="n">
-        <v>25.6</v>
+        <v>25.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.782</v>
+        <v>0.783</v>
       </c>
       <c r="R17" t="n">
         <v>12.1</v>
       </c>
       <c r="S17" t="n">
-        <v>29</v>
+        <v>28.8</v>
       </c>
       <c r="T17" t="n">
-        <v>41.1</v>
+        <v>40.9</v>
       </c>
       <c r="U17" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="V17" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W17" t="n">
         <v>7.3</v>
@@ -3457,10 +3524,10 @@
         <v>4.7</v>
       </c>
       <c r="Z17" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="AB17" t="n">
         <v>99.09999999999999</v>
@@ -3469,10 +3536,10 @@
         <v>-1.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF17" t="n">
         <v>19</v>
@@ -3481,16 +3548,16 @@
         <v>19</v>
       </c>
       <c r="AH17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ17" t="n">
         <v>8</v>
       </c>
       <c r="AK17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL17" t="n">
         <v>21</v>
@@ -3502,10 +3569,10 @@
         <v>19</v>
       </c>
       <c r="AO17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ17" t="n">
         <v>11</v>
@@ -3514,25 +3581,25 @@
         <v>5</v>
       </c>
       <c r="AS17" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AT17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU17" t="n">
         <v>9</v>
       </c>
       <c r="AV17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX17" t="n">
         <v>29</v>
       </c>
       <c r="AY17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ17" t="n">
         <v>30</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-27-2008-09</t>
+          <t>2009-03-27</t>
         </is>
       </c>
     </row>
@@ -3573,28 +3640,28 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E18" t="n">
         <v>20</v>
       </c>
       <c r="F18" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G18" t="n">
-        <v>0.274</v>
+        <v>0.278</v>
       </c>
       <c r="H18" t="n">
         <v>48.3</v>
       </c>
       <c r="I18" t="n">
-        <v>36.4</v>
+        <v>36.5</v>
       </c>
       <c r="J18" t="n">
-        <v>82.7</v>
+        <v>82.8</v>
       </c>
       <c r="K18" t="n">
-        <v>0.44</v>
+        <v>0.441</v>
       </c>
       <c r="L18" t="n">
         <v>6.5</v>
@@ -3603,31 +3670,31 @@
         <v>18.6</v>
       </c>
       <c r="N18" t="n">
-        <v>0.351</v>
+        <v>0.35</v>
       </c>
       <c r="O18" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="P18" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.769</v>
+        <v>0.771</v>
       </c>
       <c r="R18" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S18" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="T18" t="n">
-        <v>41.6</v>
+        <v>41.8</v>
       </c>
       <c r="U18" t="n">
         <v>20.2</v>
       </c>
       <c r="V18" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W18" t="n">
         <v>6.2</v>
@@ -3639,19 +3706,19 @@
         <v>6.1</v>
       </c>
       <c r="Z18" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AA18" t="n">
         <v>20.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>98.09999999999999</v>
+        <v>98.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>-5</v>
+        <v>-4.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE18" t="n">
         <v>25</v>
@@ -3666,13 +3733,13 @@
         <v>18</v>
       </c>
       <c r="AI18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ18" t="n">
         <v>7</v>
       </c>
       <c r="AK18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL18" t="n">
         <v>18</v>
@@ -3681,22 +3748,22 @@
         <v>15</v>
       </c>
       <c r="AN18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ18" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AR18" t="n">
         <v>7</v>
       </c>
       <c r="AS18" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AT18" t="n">
         <v>13</v>
@@ -3720,10 +3787,10 @@
         <v>22</v>
       </c>
       <c r="BA18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC18" t="n">
         <v>25</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-27-2008-09</t>
+          <t>2009-03-27</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E19" t="n">
         <v>30</v>
       </c>
       <c r="F19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G19" t="n">
-        <v>0.417</v>
+        <v>0.423</v>
       </c>
       <c r="H19" t="n">
         <v>48.4</v>
@@ -3776,40 +3843,40 @@
         <v>80</v>
       </c>
       <c r="K19" t="n">
-        <v>0.449</v>
+        <v>0.448</v>
       </c>
       <c r="L19" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="M19" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0.379</v>
+        <v>0.38</v>
       </c>
       <c r="O19" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="P19" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.779</v>
+        <v>0.782</v>
       </c>
       <c r="R19" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="S19" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="T19" t="n">
-        <v>39.8</v>
+        <v>39.7</v>
       </c>
       <c r="U19" t="n">
         <v>19.9</v>
       </c>
       <c r="V19" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="W19" t="n">
         <v>7</v>
@@ -3827,25 +3894,25 @@
         <v>20.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>98.59999999999999</v>
+        <v>98.7</v>
       </c>
       <c r="AC19" t="n">
-        <v>-2.4</v>
+        <v>-2.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AE19" t="n">
         <v>20</v>
       </c>
       <c r="AF19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG19" t="n">
         <v>20</v>
       </c>
       <c r="AH19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI19" t="n">
         <v>26</v>
@@ -3857,7 +3924,7 @@
         <v>23</v>
       </c>
       <c r="AL19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM19" t="n">
         <v>4</v>
@@ -3866,7 +3933,7 @@
         <v>8</v>
       </c>
       <c r="AO19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP19" t="n">
         <v>18</v>
@@ -3887,16 +3954,16 @@
         <v>26</v>
       </c>
       <c r="AV19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AW19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ19" t="n">
         <v>25</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-27-2008-09</t>
+          <t>2009-03-27</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E20" t="n">
         <v>44</v>
       </c>
       <c r="F20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G20" t="n">
-        <v>0.62</v>
+        <v>0.629</v>
       </c>
       <c r="H20" t="n">
         <v>48.1</v>
@@ -3955,10 +4022,10 @@
         <v>35.2</v>
       </c>
       <c r="J20" t="n">
-        <v>77.2</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>0.456</v>
+        <v>0.457</v>
       </c>
       <c r="L20" t="n">
         <v>7</v>
@@ -3967,16 +4034,16 @@
         <v>19</v>
       </c>
       <c r="N20" t="n">
-        <v>0.368</v>
+        <v>0.369</v>
       </c>
       <c r="O20" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="P20" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="R20" t="n">
         <v>9.9</v>
@@ -3988,13 +4055,13 @@
         <v>39.9</v>
       </c>
       <c r="U20" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="V20" t="n">
         <v>12.8</v>
       </c>
       <c r="W20" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X20" t="n">
         <v>4.3</v>
@@ -4003,28 +4070,28 @@
         <v>3.6</v>
       </c>
       <c r="Z20" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AA20" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>95.8</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AE20" t="n">
         <v>9</v>
       </c>
       <c r="AF20" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AG20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH20" t="n">
         <v>28</v>
@@ -4036,7 +4103,7 @@
         <v>28</v>
       </c>
       <c r="AK20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL20" t="n">
         <v>10</v>
@@ -4048,7 +4115,7 @@
         <v>14</v>
       </c>
       <c r="AO20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP20" t="n">
         <v>27</v>
@@ -4072,7 +4139,7 @@
         <v>5</v>
       </c>
       <c r="AW20" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AX20" t="n">
         <v>23</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-27-2008-09</t>
+          <t>2009-03-27</t>
         </is>
       </c>
     </row>
@@ -4119,31 +4186,31 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F21" t="n">
         <v>43</v>
       </c>
       <c r="G21" t="n">
-        <v>0.403</v>
+        <v>0.394</v>
       </c>
       <c r="H21" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I21" t="n">
         <v>38.6</v>
       </c>
       <c r="J21" t="n">
-        <v>86.8</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>0.445</v>
+        <v>0.444</v>
       </c>
       <c r="L21" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="M21" t="n">
         <v>28.4</v>
@@ -4155,16 +4222,16 @@
         <v>18.5</v>
       </c>
       <c r="P21" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.788</v>
+        <v>0.786</v>
       </c>
       <c r="R21" t="n">
         <v>11.2</v>
       </c>
       <c r="S21" t="n">
-        <v>31.2</v>
+        <v>31.1</v>
       </c>
       <c r="T21" t="n">
         <v>42.3</v>
@@ -4185,19 +4252,19 @@
         <v>5.3</v>
       </c>
       <c r="Z21" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AA21" t="n">
         <v>19.6</v>
       </c>
       <c r="AB21" t="n">
-        <v>105.9</v>
+        <v>106</v>
       </c>
       <c r="AC21" t="n">
-        <v>-2.5</v>
+        <v>-2.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AE21" t="n">
         <v>22</v>
@@ -4218,10 +4285,10 @@
         <v>1</v>
       </c>
       <c r="AK21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM21" t="n">
         <v>1</v>
@@ -4236,16 +4303,16 @@
         <v>21</v>
       </c>
       <c r="AQ21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR21" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AS21" t="n">
         <v>8</v>
       </c>
       <c r="AT21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU21" t="n">
         <v>11</v>
@@ -4254,7 +4321,7 @@
         <v>18</v>
       </c>
       <c r="AW21" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4263,10 +4330,10 @@
         <v>22</v>
       </c>
       <c r="AZ21" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA21" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BB21" t="n">
         <v>4</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-27-2008-09</t>
+          <t>2009-03-27</t>
         </is>
       </c>
     </row>
@@ -4301,19 +4368,19 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E22" t="n">
         <v>20</v>
       </c>
       <c r="F22" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G22" t="n">
-        <v>0.278</v>
+        <v>0.282</v>
       </c>
       <c r="H22" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I22" t="n">
         <v>36.6</v>
@@ -4322,7 +4389,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>0.447</v>
+        <v>0.448</v>
       </c>
       <c r="L22" t="n">
         <v>4.1</v>
@@ -4331,13 +4398,13 @@
         <v>11.8</v>
       </c>
       <c r="N22" t="n">
-        <v>0.347</v>
+        <v>0.349</v>
       </c>
       <c r="O22" t="n">
         <v>20</v>
       </c>
       <c r="P22" t="n">
-        <v>25.5</v>
+        <v>25.4</v>
       </c>
       <c r="Q22" t="n">
         <v>0.787</v>
@@ -4349,13 +4416,13 @@
         <v>30.5</v>
       </c>
       <c r="T22" t="n">
-        <v>42.9</v>
+        <v>43</v>
       </c>
       <c r="U22" t="n">
         <v>20.1</v>
       </c>
       <c r="V22" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="W22" t="n">
         <v>7.3</v>
@@ -4364,22 +4431,22 @@
         <v>4.4</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AA22" t="n">
         <v>20.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>97.3</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AC22" t="n">
-        <v>-5.6</v>
+        <v>-5.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AE22" t="n">
         <v>25</v>
@@ -4394,7 +4461,7 @@
         <v>15</v>
       </c>
       <c r="AI22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ22" t="n">
         <v>9</v>
@@ -4409,7 +4476,7 @@
         <v>30</v>
       </c>
       <c r="AN22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO22" t="n">
         <v>6</v>
@@ -4418,25 +4485,25 @@
         <v>11</v>
       </c>
       <c r="AQ22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT22" t="n">
         <v>4</v>
       </c>
-      <c r="AS22" t="n">
-        <v>13</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>5</v>
-      </c>
       <c r="AU22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV22" t="n">
         <v>30</v>
       </c>
       <c r="AW22" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AX22" t="n">
         <v>22</v>
@@ -4445,7 +4512,7 @@
         <v>17</v>
       </c>
       <c r="AZ22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA22" t="n">
         <v>20</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-27-2008-09</t>
+          <t>2009-03-27</t>
         </is>
       </c>
     </row>
@@ -4483,22 +4550,22 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E23" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F23" t="n">
         <v>18</v>
       </c>
       <c r="G23" t="n">
-        <v>0.75</v>
+        <v>0.746</v>
       </c>
       <c r="H23" t="n">
         <v>48.1</v>
       </c>
       <c r="I23" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="J23" t="n">
         <v>78.2</v>
@@ -4510,19 +4577,19 @@
         <v>10.3</v>
       </c>
       <c r="M23" t="n">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="N23" t="n">
-        <v>0.387</v>
+        <v>0.386</v>
       </c>
       <c r="O23" t="n">
         <v>19.9</v>
       </c>
       <c r="P23" t="n">
-        <v>27.6</v>
+        <v>27.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.721</v>
+        <v>0.723</v>
       </c>
       <c r="R23" t="n">
         <v>10</v>
@@ -4537,10 +4604,10 @@
         <v>19.5</v>
       </c>
       <c r="V23" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W23" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X23" t="n">
         <v>5.4</v>
@@ -4552,19 +4619,19 @@
         <v>20.3</v>
       </c>
       <c r="AA23" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>102.2</v>
+        <v>102.1</v>
       </c>
       <c r="AC23" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AE23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF23" t="n">
         <v>3</v>
@@ -4582,7 +4649,7 @@
         <v>26</v>
       </c>
       <c r="AK23" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AL23" t="n">
         <v>1</v>
@@ -4603,7 +4670,7 @@
         <v>30</v>
       </c>
       <c r="AR23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS23" t="n">
         <v>1</v>
@@ -4615,7 +4682,7 @@
         <v>29</v>
       </c>
       <c r="AV23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW23" t="n">
         <v>20</v>
@@ -4627,7 +4694,7 @@
         <v>2</v>
       </c>
       <c r="AZ23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA23" t="n">
         <v>5</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-27-2008-09</t>
+          <t>2009-03-27</t>
         </is>
       </c>
     </row>
@@ -4665,25 +4732,25 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E24" t="n">
         <v>37</v>
       </c>
       <c r="F24" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G24" t="n">
-        <v>0.521</v>
+        <v>0.529</v>
       </c>
       <c r="H24" t="n">
         <v>48.1</v>
       </c>
       <c r="I24" t="n">
-        <v>36.7</v>
+        <v>36.8</v>
       </c>
       <c r="J24" t="n">
-        <v>80.09999999999999</v>
+        <v>80.3</v>
       </c>
       <c r="K24" t="n">
         <v>0.459</v>
@@ -4695,28 +4762,28 @@
         <v>13.1</v>
       </c>
       <c r="N24" t="n">
-        <v>0.32</v>
+        <v>0.321</v>
       </c>
       <c r="O24" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="P24" t="n">
-        <v>26.6</v>
+        <v>26.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.745</v>
+        <v>0.744</v>
       </c>
       <c r="R24" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="S24" t="n">
-        <v>29</v>
+        <v>29.2</v>
       </c>
       <c r="T24" t="n">
-        <v>41.6</v>
+        <v>41.9</v>
       </c>
       <c r="U24" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="V24" t="n">
         <v>14.4</v>
@@ -4734,16 +4801,16 @@
         <v>20.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="AB24" t="n">
         <v>97.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AE24" t="n">
         <v>15</v>
@@ -4752,16 +4819,16 @@
         <v>14</v>
       </c>
       <c r="AG24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH24" t="n">
         <v>24</v>
       </c>
       <c r="AI24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK24" t="n">
         <v>13</v>
@@ -4776,7 +4843,7 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AP24" t="n">
         <v>6</v>
@@ -4791,10 +4858,10 @@
         <v>22</v>
       </c>
       <c r="AT24" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AU24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV24" t="n">
         <v>17</v>
@@ -4806,7 +4873,7 @@
         <v>11</v>
       </c>
       <c r="AY24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ24" t="n">
         <v>6</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-27-2008-09</t>
+          <t>2009-03-27</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>2.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE25" t="n">
         <v>13</v>
@@ -4937,7 +5004,7 @@
         <v>13</v>
       </c>
       <c r="AH25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI25" t="n">
         <v>1</v>
@@ -4964,7 +5031,7 @@
         <v>5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR25" t="n">
         <v>22</v>
@@ -4973,16 +5040,16 @@
         <v>10</v>
       </c>
       <c r="AT25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU25" t="n">
         <v>3</v>
       </c>
       <c r="AV25" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AW25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX25" t="n">
         <v>12</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-27-2008-09</t>
+          <t>2009-03-27</t>
         </is>
       </c>
     </row>
@@ -5029,52 +5096,52 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E26" t="n">
         <v>45</v>
       </c>
       <c r="F26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G26" t="n">
-        <v>0.634</v>
+        <v>0.625</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="J26" t="n">
-        <v>79.3</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>0.463</v>
+        <v>0.462</v>
       </c>
       <c r="L26" t="n">
         <v>7.3</v>
       </c>
       <c r="M26" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="N26" t="n">
         <v>0.38</v>
       </c>
       <c r="O26" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="P26" t="n">
-        <v>24.5</v>
+        <v>24.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.77</v>
+        <v>0.768</v>
       </c>
       <c r="R26" t="n">
         <v>12.9</v>
       </c>
       <c r="S26" t="n">
-        <v>28.4</v>
+        <v>28.5</v>
       </c>
       <c r="T26" t="n">
         <v>41.3</v>
@@ -5092,37 +5159,37 @@
         <v>4.9</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Z26" t="n">
         <v>20.6</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.59999999999999</v>
+        <v>99.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="AE26" t="n">
         <v>8</v>
       </c>
       <c r="AF26" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AG26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ26" t="n">
         <v>22</v>
@@ -5140,13 +5207,13 @@
         <v>7</v>
       </c>
       <c r="AO26" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP26" t="n">
         <v>17</v>
       </c>
-      <c r="AP26" t="n">
-        <v>16</v>
-      </c>
       <c r="AQ26" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AR26" t="n">
         <v>1</v>
@@ -5158,10 +5225,10 @@
         <v>16</v>
       </c>
       <c r="AU26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW26" t="n">
         <v>26</v>
@@ -5173,7 +5240,7 @@
         <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA26" t="n">
         <v>12</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-27-2008-09</t>
+          <t>2009-03-27</t>
         </is>
       </c>
     </row>
@@ -5211,25 +5278,25 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E27" t="n">
         <v>15</v>
       </c>
       <c r="F27" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G27" t="n">
-        <v>0.211</v>
+        <v>0.214</v>
       </c>
       <c r="H27" t="n">
         <v>48.6</v>
       </c>
       <c r="I27" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="J27" t="n">
-        <v>80.8</v>
+        <v>81</v>
       </c>
       <c r="K27" t="n">
         <v>0.448</v>
@@ -5241,13 +5308,13 @@
         <v>19.1</v>
       </c>
       <c r="N27" t="n">
-        <v>0.363</v>
+        <v>0.364</v>
       </c>
       <c r="O27" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="P27" t="n">
-        <v>25.7</v>
+        <v>25.5</v>
       </c>
       <c r="Q27" t="n">
         <v>0.804</v>
@@ -5256,16 +5323,16 @@
         <v>10</v>
       </c>
       <c r="S27" t="n">
-        <v>28.7</v>
+        <v>28.8</v>
       </c>
       <c r="T27" t="n">
-        <v>38.6</v>
+        <v>38.8</v>
       </c>
       <c r="U27" t="n">
         <v>19.7</v>
       </c>
       <c r="V27" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="W27" t="n">
         <v>7.1</v>
@@ -5274,22 +5341,22 @@
         <v>4</v>
       </c>
       <c r="Y27" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z27" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="AA27" t="n">
         <v>21.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="AC27" t="n">
-        <v>-8.6</v>
+        <v>-8.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AE27" t="n">
         <v>30</v>
@@ -5307,7 +5374,7 @@
         <v>23</v>
       </c>
       <c r="AJ27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK27" t="n">
         <v>24</v>
@@ -5325,13 +5392,13 @@
         <v>4</v>
       </c>
       <c r="AP27" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AQ27" t="n">
         <v>6</v>
       </c>
       <c r="AR27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS27" t="n">
         <v>27</v>
@@ -5343,19 +5410,19 @@
         <v>27</v>
       </c>
       <c r="AV27" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AW27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX27" t="n">
         <v>28</v>
       </c>
       <c r="AY27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA27" t="n">
         <v>11</v>
@@ -5364,7 +5431,7 @@
         <v>13</v>
       </c>
       <c r="BC27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-27-2008-09</t>
+          <t>2009-03-27</t>
         </is>
       </c>
     </row>
@@ -5393,46 +5460,46 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E28" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F28" t="n">
         <v>24</v>
       </c>
       <c r="G28" t="n">
-        <v>0.667</v>
+        <v>0.662</v>
       </c>
       <c r="H28" t="n">
         <v>48.6</v>
       </c>
       <c r="I28" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="J28" t="n">
-        <v>79.7</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.466</v>
+        <v>0.465</v>
       </c>
       <c r="L28" t="n">
         <v>7.7</v>
       </c>
       <c r="M28" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="N28" t="n">
         <v>0.392</v>
       </c>
       <c r="O28" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="P28" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.765</v>
+        <v>0.764</v>
       </c>
       <c r="R28" t="n">
         <v>8.699999999999999</v>
@@ -5444,13 +5511,13 @@
         <v>41</v>
       </c>
       <c r="U28" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="V28" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="W28" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="X28" t="n">
         <v>4.2</v>
@@ -5462,16 +5529,16 @@
         <v>18.7</v>
       </c>
       <c r="AA28" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>97</v>
+        <v>96.8</v>
       </c>
       <c r="AC28" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AE28" t="n">
         <v>5</v>
@@ -5483,7 +5550,7 @@
         <v>5</v>
       </c>
       <c r="AH28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI28" t="n">
         <v>10</v>
@@ -5501,7 +5568,7 @@
         <v>9</v>
       </c>
       <c r="AN28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO28" t="n">
         <v>30</v>
@@ -5519,13 +5586,13 @@
         <v>3</v>
       </c>
       <c r="AT28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AV28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW28" t="n">
         <v>30</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-27-2008-09</t>
+          <t>2009-03-27</t>
         </is>
       </c>
     </row>
@@ -5575,28 +5642,28 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F29" t="n">
         <v>45</v>
       </c>
       <c r="G29" t="n">
-        <v>0.375</v>
+        <v>0.366</v>
       </c>
       <c r="H29" t="n">
         <v>48.3</v>
       </c>
       <c r="I29" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="J29" t="n">
-        <v>80.2</v>
+        <v>80</v>
       </c>
       <c r="K29" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L29" t="n">
         <v>5.9</v>
@@ -5605,28 +5672,28 @@
         <v>15.8</v>
       </c>
       <c r="N29" t="n">
-        <v>0.374</v>
+        <v>0.373</v>
       </c>
       <c r="O29" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="P29" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.827</v>
+        <v>0.826</v>
       </c>
       <c r="R29" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S29" t="n">
-        <v>30.7</v>
+        <v>30.5</v>
       </c>
       <c r="T29" t="n">
-        <v>39.9</v>
+        <v>39.7</v>
       </c>
       <c r="U29" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="V29" t="n">
         <v>13.4</v>
@@ -5644,16 +5711,16 @@
         <v>19.3</v>
       </c>
       <c r="AA29" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AB29" t="n">
-        <v>98</v>
+        <v>97.8</v>
       </c>
       <c r="AC29" t="n">
-        <v>-3</v>
+        <v>-3.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AE29" t="n">
         <v>23</v>
@@ -5665,16 +5732,16 @@
         <v>23</v>
       </c>
       <c r="AH29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI29" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AJ29" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AK29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL29" t="n">
         <v>24</v>
@@ -5686,10 +5753,10 @@
         <v>11</v>
       </c>
       <c r="AO29" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AP29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ29" t="n">
         <v>1</v>
@@ -5701,10 +5768,10 @@
         <v>11</v>
       </c>
       <c r="AT29" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AU29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV29" t="n">
         <v>10</v>
@@ -5713,7 +5780,7 @@
         <v>28</v>
       </c>
       <c r="AX29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY29" t="n">
         <v>11</v>
@@ -5722,7 +5789,7 @@
         <v>3</v>
       </c>
       <c r="BA29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB29" t="n">
         <v>21</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-27-2008-09</t>
+          <t>2009-03-27</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>3.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AE30" t="n">
         <v>9</v>
@@ -5844,7 +5911,7 @@
         <v>9</v>
       </c>
       <c r="AG30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH30" t="n">
         <v>8</v>
@@ -5853,7 +5920,7 @@
         <v>6</v>
       </c>
       <c r="AJ30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK30" t="n">
         <v>4</v>
@@ -5880,7 +5947,7 @@
         <v>9</v>
       </c>
       <c r="AS30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT30" t="n">
         <v>17</v>
@@ -5898,7 +5965,7 @@
         <v>15</v>
       </c>
       <c r="AY30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ30" t="n">
         <v>23</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-27-2008-09</t>
+          <t>2009-03-27</t>
         </is>
       </c>
     </row>
@@ -6020,16 +6087,16 @@
         <v>1</v>
       </c>
       <c r="AE31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF31" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG31" t="n">
         <v>29</v>
       </c>
       <c r="AH31" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI31" t="n">
         <v>20</v>
@@ -6068,7 +6135,7 @@
         <v>24</v>
       </c>
       <c r="AU31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AV31" t="n">
         <v>12</v>
@@ -6086,7 +6153,7 @@
         <v>14</v>
       </c>
       <c r="BA31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BB31" t="n">
         <v>27</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-27-2008-09</t>
+          <t>2009-03-27</t>
         </is>
       </c>
     </row>
